--- a/timeTable_ME.xlsx
+++ b/timeTable_ME.xlsx
@@ -1,67 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\Python\tempWorkSpace\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drlak\my_projects\projects_myTimetable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1DE659D-16BE-40E0-A1E6-9BF5D3B29C05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B1180DC-3360-402F-A195-E61FF643FD5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="690" yWindow="1020" windowWidth="15315" windowHeight="7800" activeTab="7" xr2:uid="{7BEB5D9E-8563-4ED7-B850-B47E02154E05}"/>
+    <workbookView xWindow="3930" yWindow="4005" windowWidth="19290" windowHeight="10755" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="s1" sheetId="1" r:id="rId1"/>
-    <sheet name="s2" sheetId="2" r:id="rId2"/>
-    <sheet name="s3" sheetId="3" r:id="rId3"/>
-    <sheet name="s4" sheetId="4" r:id="rId4"/>
-    <sheet name="s5" sheetId="6" r:id="rId5"/>
-    <sheet name="s6" sheetId="7" r:id="rId6"/>
-    <sheet name="s7" sheetId="8" r:id="rId7"/>
-    <sheet name="s8" sheetId="9" r:id="rId8"/>
+    <sheet name="s2" sheetId="1" r:id="rId1"/>
+    <sheet name="s3" sheetId="2" r:id="rId2"/>
+    <sheet name="s4" sheetId="3" r:id="rId3"/>
+    <sheet name="s5" sheetId="4" r:id="rId4"/>
+    <sheet name="s6" sheetId="5" r:id="rId5"/>
+    <sheet name="s7" sheetId="6" r:id="rId6"/>
+    <sheet name="s8" sheetId="7" r:id="rId7"/>
+    <sheet name="s1" sheetId="8" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="16">
   <si>
-    <t>monday</t>
-  </si>
-  <si>
-    <t>tuesday</t>
-  </si>
-  <si>
-    <t>wednesday</t>
-  </si>
-  <si>
-    <t>thursday</t>
-  </si>
-  <si>
-    <t>friday</t>
+    <t>week_day</t>
   </si>
   <si>
     <t>slot_1</t>
-  </si>
-  <si>
-    <t>week_day</t>
   </si>
   <si>
     <t>slot_2</t>
@@ -82,119 +53,44 @@
     <t>slot_x</t>
   </si>
   <si>
-    <t>mon_s1[]</t>
+    <t>monday</t>
   </si>
   <si>
-    <t>mon_s2[]</t>
+    <t>GAMAT101</t>
   </si>
   <si>
-    <t>mon_s3[]</t>
+    <t>GAPHT121</t>
   </si>
   <si>
-    <t>mon_s4[]</t>
+    <t>FREE</t>
   </si>
   <si>
-    <t>mon_s5[]</t>
+    <t>tuesday</t>
   </si>
   <si>
-    <t>mon_s6[]</t>
+    <t>wednesday</t>
   </si>
   <si>
-    <t>mon_sx[]</t>
+    <t>thursday</t>
   </si>
   <si>
-    <t>tue_s1[]</t>
-  </si>
-  <si>
-    <t>tue_s2[]</t>
-  </si>
-  <si>
-    <t>tue_s3[]</t>
-  </si>
-  <si>
-    <t>tue_s4[]</t>
-  </si>
-  <si>
-    <t>tue_s5[]</t>
-  </si>
-  <si>
-    <t>tue_s6[]</t>
-  </si>
-  <si>
-    <t>tue_sx[]</t>
-  </si>
-  <si>
-    <t>wed_s1[]</t>
-  </si>
-  <si>
-    <t>wed_s2[]</t>
-  </si>
-  <si>
-    <t>wed_s3[]</t>
-  </si>
-  <si>
-    <t>wed_s4[]</t>
-  </si>
-  <si>
-    <t>wed_s5[]</t>
-  </si>
-  <si>
-    <t>wed_s6[]</t>
-  </si>
-  <si>
-    <t>wed_sx[]</t>
-  </si>
-  <si>
-    <t>thu_s1[]</t>
-  </si>
-  <si>
-    <t>thu_s2[]</t>
-  </si>
-  <si>
-    <t>thu_s3[]</t>
-  </si>
-  <si>
-    <t>thu_s4[]</t>
-  </si>
-  <si>
-    <t>thu_s5[]</t>
-  </si>
-  <si>
-    <t>thu_s6[]</t>
-  </si>
-  <si>
-    <t>thu_sx[]</t>
-  </si>
-  <si>
-    <t>fri_s1[]</t>
-  </si>
-  <si>
-    <t>fri_s2[]</t>
-  </si>
-  <si>
-    <t>fri_s3[]</t>
-  </si>
-  <si>
-    <t>fri_s4[]</t>
-  </si>
-  <si>
-    <t>fri_s5[]</t>
-  </si>
-  <si>
-    <t>fri_s6[]</t>
-  </si>
-  <si>
-    <t>fri_sx[]</t>
+    <t>friday</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -538,338 +434,330 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B2FF754-53A3-456E-8EC4-F40BFA0EB238}">
-  <dimension ref="A1:H23"/>
-  <sheetFormatPr defaultColWidth="10.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G5" t="s">
-        <v>39</v>
-      </c>
-      <c r="H5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" t="s">
-        <v>42</v>
-      </c>
-      <c r="D6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F6" t="s">
-        <v>45</v>
-      </c>
-      <c r="G6" t="s">
-        <v>46</v>
-      </c>
-      <c r="H6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="18" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="19" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="20" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="21" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="22" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="23" customFormat="1" x14ac:dyDescent="0.25"/>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C110C39-E9A8-412D-BA79-F791A8C11156}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H6"/>
   <sheetFormatPr defaultColWidth="10.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H2" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="G3" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="H3" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G4" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H4" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="G5" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="H5" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr defaultColWidth="10.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:8" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
       <c r="B6" t="s">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="G6" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="H6" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -878,164 +766,164 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{016073B4-58F2-46EA-95FF-CB5DF214BB37}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H6"/>
   <sheetFormatPr defaultColWidth="10.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H2" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="G3" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="H3" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G4" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H4" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="G5" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="H5" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="G6" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="H6" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1044,164 +932,164 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B97E712-1FDA-4609-8BB8-057B439A0A11}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:H6"/>
   <sheetFormatPr defaultColWidth="10.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H2" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="G3" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="H3" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G4" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H4" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="G5" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="H5" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="G6" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="H6" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1210,164 +1098,331 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C21AB53-9624-4622-BF1F-49EF41960459}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:H6"/>
   <sheetFormatPr defaultColWidth="10.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H2" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="G3" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="H3" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G4" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H4" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="G5" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="H5" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr defaultColWidth="10.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:8" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
       <c r="B6" t="s">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="G6" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="H6" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1375,332 +1430,165 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DAD63D9-991E-46ED-979E-9B38925B6A2E}">
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultColWidth="10.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H2" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="G3" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="H3" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G4" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H4" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="G5" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="H5" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="G6" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="H6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C1D549B-B3E8-407F-8594-6DBABB4D89B9}">
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultColWidth="10.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G5" t="s">
-        <v>39</v>
-      </c>
-      <c r="H5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" t="s">
-        <v>42</v>
-      </c>
-      <c r="D6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F6" t="s">
-        <v>45</v>
-      </c>
-      <c r="G6" t="s">
-        <v>46</v>
-      </c>
-      <c r="H6" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1709,174 +1597,168 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5407EBD7-2E39-401C-A46B-5C53E0C7EE30}">
-  <dimension ref="A1:H23"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultColWidth="10.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H2" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="G3" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="H3" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G4" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H4" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="G5" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="H5" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="G6" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="H6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="18" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="19" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="20" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="21" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="22" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="23" customFormat="1" x14ac:dyDescent="0.25"/>
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>